--- a/sources/ling_step6b.xlsx
+++ b/sources/ling_step6b.xlsx
@@ -423,7 +423,7 @@
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -7375,12 +7375,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>4 [~B]</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Flower Kick [RDS]</t>
+          <t>Flower Kick</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>(~B)RDS</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7432,12 +7437,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>4~3 [u_d]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Fire Cracker - [Roll up or down]</t>
+          <t>Fire Cracker</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>(~U)Quick roll to background; (~D)Quick roll to foreground</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -7986,7 +7996,7 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">

--- a/sources/ling_step6b.xlsx
+++ b/sources/ling_step6b.xlsx
@@ -904,6 +904,11 @@
           <t>Which throw is done depends on the position. Use the proper escape command depending on the throw.</t>
         </is>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>a24bf04e-0d2e-4145-8a90-082242d8b227</t>
@@ -956,6 +961,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>50a70a48-afe6-40fd-8f35-16ca8bff01a0</t>
@@ -1003,6 +1013,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>4907eee5-3efc-44a2-a055-d184d67b1678</t>
@@ -1048,6 +1063,11 @@
       <c r="M12" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>cb6c831f-06d3-4000-b9f7-9fd513e65128</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -8193,6 +8213,11 @@
           <t>mhhmmMLLmm</t>
         </is>
       </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
+        </is>
+      </c>
       <c r="R149" t="inlineStr">
         <is>
           <t>d6eeaf40-1498-4551-b18c-5d04a4263947</t>
@@ -8223,6 +8248,11 @@
       <c r="K150" t="inlineStr">
         <is>
           <t>mhhLLmmllmm</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>a77680ba-55cb-467b-b7b3-7b9a5ced7ee7</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
